--- a/artfynd/S 3570-2025 artfynd.xlsx
+++ b/artfynd/S 3570-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6970555</v>
+        <v>137541482</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>98102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,48 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219788</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österbo, NNO 375 m, Vstm</t>
+          <t>Ljungkullen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>533064</v>
+        <v>532775</v>
       </c>
       <c r="R4" t="n">
-        <v>6640851</v>
+        <v>6641692</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,17 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>De två(?) bladen helt utan fläckar. Lite märkligt att det bara var en enda blommande planta.</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,72 +978,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kärr</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britt Halling, Sven-Arne Örn, Bengt Stridh</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6970555</t>
+          <t>https://artportalen.se/Sighting/137541482</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6970533</v>
+        <v>137541593</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Österbo, NNO 325 m, Vstm</t>
+          <t>Ljungkullen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>533034</v>
+        <v>532681</v>
       </c>
       <c r="R5" t="n">
-        <v>6640803</v>
+        <v>6641830</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,17 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tiotals blommande</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,77 +1085,77 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kärr</t>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Stridh</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britt Halling, Sven-Arne Örn, Bengt Stridh</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6970533</t>
+          <t>https://artportalen.se/Sighting/137541593</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>25916</v>
+        <v>137541594</v>
       </c>
       <c r="B6" t="n">
-        <v>58826</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208242</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Darsbo hage, Vstm</t>
+          <t>Ljungkullen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538123</v>
+        <v>532657</v>
       </c>
       <c r="R6" t="n">
-        <v>6640792</v>
+        <v>6641853</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,12 +1179,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2001-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2001-05-18</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,35 +1195,40 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karin Andersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Norman</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för större vattensalamander</t>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/25916</t>
+          <t>https://artportalen.se/Sighting/137541594</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102542885</v>
+        <v>137541422</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>79563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,47 +1236,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6434</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormdalen, Skinnskatteberg, Vstm</t>
+          <t>Ljungkullen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529118</v>
+        <v>532700</v>
       </c>
       <c r="R7" t="n">
-        <v>6639773</v>
+        <v>6641820</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,22 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-07-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:28</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,31 +1306,40 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joa Niskakari</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joa Niskakari</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102542885</t>
+          <t>https://artportalen.se/Sighting/137541422</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>86916199</v>
+        <v>6970555</v>
       </c>
       <c r="B8" t="n">
-        <v>91872</v>
+        <v>99026</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,40 +1347,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>219788</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Timmeråsarna, Vstm</t>
+          <t>Österbo, NNO 375 m, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525607</v>
+        <v>533064</v>
       </c>
       <c r="R8" t="n">
-        <v>6638892</v>
+        <v>6640851</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,12 +1415,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-09-19</t>
+          <t>2013-06-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-10-19</t>
+          <t>2013-06-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>De två(?) bladen helt utan fläckar. Lite märkligt att det bara var en enda blommande planta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,79 +1434,74 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Äldre barrskog, höjdlägeskaraktär</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Liggande granstam</t>
+          <t>Kärr</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Britt Halling, Sven-Arne Örn, Bengt Stridh</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86916199</t>
+          <t>https://artportalen.se/Sighting/6970555</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100566</v>
+        <v>6970533</v>
       </c>
       <c r="B9" t="n">
-        <v>97358</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>223597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vattuberget, Vstm</t>
+          <t>Österbo, NNO 325 m, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>527133</v>
+        <v>533034</v>
       </c>
       <c r="R9" t="n">
-        <v>6639175</v>
+        <v>6640803</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,17 +1528,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
+          <t>2013-06-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-12-31</t>
+          <t>2013-06-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Naturvårdsinventering</t>
+          <t>Tiotals blommande</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,31 +1550,35 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AR9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kärr</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Bengt Stridh</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Britt Halling, Sven-Arne Örn, Bengt Stridh</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100566</t>
+          <t>https://artportalen.se/Sighting/6970533</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133859345</v>
+        <v>25916</v>
       </c>
       <c r="B10" t="n">
-        <v>96413</v>
+        <v>58826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,41 +1586,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>208242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vattuberget, Ribäcken , Vstm</t>
+          <t>Darsbo hage, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>527044</v>
+        <v>538123</v>
       </c>
       <c r="R10" t="n">
-        <v>6638882</v>
+        <v>6640792</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,22 +1644,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2001-05-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2001-05-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,65 +1664,79 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Karin Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Anna Norman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för större vattensalamander</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133859345</t>
+          <t>https://artportalen.se/Sighting/25916</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1862856</v>
+        <v>102542885</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vattuberget, Vstm</t>
+          <t>Ormdalen, Skinnskatteberg, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526903</v>
+        <v>529118</v>
       </c>
       <c r="R11" t="n">
-        <v>6638998</v>
+        <v>6639773</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1773,17 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2012-12-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Naturvårdsinventering</t>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,31 +1787,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Joa Niskakari</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
+          <t>Joa Niskakari</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/1862856</t>
+          <t>https://artportalen.se/Sighting/102542885</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4898364</v>
+        <v>86916199</v>
       </c>
       <c r="B12" t="n">
-        <v>100143</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,37 +1818,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222467</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vattuberget, Vstm</t>
+          <t>Timmeråsarna, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526892</v>
+        <v>525607</v>
       </c>
       <c r="R12" t="n">
-        <v>6639044</v>
+        <v>6638892</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1881,17 +1875,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2012-01-01</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2012-12-31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Naturvårdsinventering</t>
+          <t>2018-10-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,14 +1889,24 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AR12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, höjdlägeskaraktär</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Liggande granstam</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -1918,63 +1917,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/4898364</t>
+          <t>https://artportalen.se/Sighting/86916199</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129496200</v>
+        <v>100566</v>
       </c>
       <c r="B13" t="n">
-        <v>99035</v>
+        <v>97358</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ribäcken, Tackbyn, Vstm</t>
+          <t>Vattuberget, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>527780</v>
+        <v>527133</v>
       </c>
       <c r="R13" t="n">
-        <v>6638454</v>
+        <v>6639175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2001,17 +1988,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>minst 100, börjar blomma.</t>
+          <t>Naturvårdsinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,34 +2007,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AR13" t="inlineStr"/>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Leif Johansson</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Eriksson, Leif Johansson</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129496200</t>
+          <t>https://artportalen.se/Sighting/100566</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6865734</v>
+        <v>133859345</v>
       </c>
       <c r="B14" t="n">
-        <v>99022</v>
+        <v>96413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,45 +2042,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220093</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tackbyn, Vstm</t>
+          <t>Vattuberget, Ribäcken , Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>527780</v>
+        <v>527044</v>
       </c>
       <c r="R14" t="n">
-        <v>6638454</v>
+        <v>6638882</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,12 +2100,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,82 +2126,66 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>rikkärr</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lasse Gustavsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lasse Gustavsson, Karin Bjerner, Anne Höglund, Einar Marklund</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6865734</t>
+          <t>https://artportalen.se/Sighting/133859345</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6865733</v>
+        <v>1862856</v>
       </c>
       <c r="B15" t="n">
-        <v>99140</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tackbyn, Vstm</t>
+          <t>Vattuberget, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>527780</v>
+        <v>526903</v>
       </c>
       <c r="R15" t="n">
-        <v>6638454</v>
+        <v>6638998</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,12 +2212,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2013-06-29</t>
+          <t>2012-12-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Naturvårdsinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,35 +2234,31 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>rikkärr</t>
-        </is>
-      </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lasse Gustavsson</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lasse Gustavsson, Karin Bjerner, Anne Höglund, Einar Marklund</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6865733</t>
+          <t>https://artportalen.se/Sighting/1862856</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>71950242</v>
+        <v>4898364</v>
       </c>
       <c r="B16" t="n">
-        <v>99140</v>
+        <v>100143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2291,46 +2266,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>222467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Limes Norrlandicus, Vstm</t>
+          <t>Vattuberget, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>527789</v>
+        <v>526892</v>
       </c>
       <c r="R16" t="n">
-        <v>6638446</v>
+        <v>6639044</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2354,17 +2320,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2015-06-26</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2015-06-26</t>
+          <t>2012-12-31</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Barbilophozia lycopodioides present</t>
+          <t>Naturvårdsinventering</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,19 +2342,492 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AR16" t="inlineStr"/>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Caroline Greiser</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Caroline Greiser</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4898364</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129496200</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ribäcken, Tackbyn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>527780</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6638454</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>minst 100, börjar blomma.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jan Eriksson, Leif Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129496200</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6865734</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tackbyn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>527780</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6638454</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2013-06-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2013-06-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>rikkärr</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lasse Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lasse Gustavsson, Karin Bjerner, Anne Höglund, Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6865734</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6865733</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tackbyn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>527780</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6638454</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2013-06-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2013-06-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>rikkärr</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lasse Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lasse Gustavsson, Karin Bjerner, Anne Höglund, Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6865733</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>71950242</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Limes Norrlandicus, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>527789</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6638446</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2015-06-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2015-06-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Barbilophozia lycopodioides present</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Caroline Greiser</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Caroline Greiser</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/71950242</t>
         </is>
@@ -2411,6 +2850,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
